--- a/diseases/d153/2005-2009.xlsx
+++ b/diseases/d153/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>42</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.8005974744580812</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>36</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.6862264066783554</v>
       </c>
@@ -2001,9 +1995,6 @@
       <c r="O9" t="n">
         <v>45</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.8577830083479442</v>
       </c>
@@ -2545,9 +2536,6 @@
       <c r="O12" t="n">
         <v>54</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>1.029339610017533</v>
       </c>
@@ -3089,9 +3077,6 @@
       <c r="O15" t="n">
         <v>45</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.8577830083479442</v>
       </c>
@@ -3633,9 +3618,6 @@
       <c r="O18" t="n">
         <v>41</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.781535629828127</v>
       </c>
@@ -4177,9 +4159,6 @@
       <c r="O21" t="n">
         <v>25</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.4765461157488579</v>
       </c>
@@ -4721,9 +4700,6 @@
       <c r="O24" t="n">
         <v>38</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.724350095938264</v>
       </c>
@@ -5265,9 +5241,6 @@
       <c r="O27" t="n">
         <v>43</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.8196593190880357</v>
       </c>
@@ -5809,9 +5782,6 @@
       <c r="O30" t="n">
         <v>42</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.8005974744580812</v>
       </c>
@@ -6353,9 +6323,6 @@
       <c r="O33" t="n">
         <v>42</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.8005974744580812</v>
       </c>
@@ -6897,9 +6864,6 @@
       <c r="O36" t="n">
         <v>41</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.781535629828127</v>
       </c>
@@ -7441,9 +7405,6 @@
       <c r="O39" t="n">
         <v>35</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.6646099836002739</v>
       </c>
@@ -7985,9 +7946,6 @@
       <c r="O42" t="n">
         <v>39</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.740565410297448</v>
       </c>
@@ -8529,9 +8487,6 @@
       <c r="O45" t="n">
         <v>33</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.6266322702516869</v>
       </c>
@@ -9073,9 +9028,6 @@
       <c r="O48" t="n">
         <v>36</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.6835988402745675</v>
       </c>
@@ -9617,9 +9569,6 @@
       <c r="O51" t="n">
         <v>37</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.702587696948861</v>
       </c>
@@ -10161,9 +10110,6 @@
       <c r="O54" t="n">
         <v>47</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.8924762636917963</v>
       </c>
@@ -10705,9 +10651,6 @@
       <c r="O57" t="n">
         <v>28</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.5316879868802191</v>
       </c>
@@ -11249,9 +11192,6 @@
       <c r="O60" t="n">
         <v>29</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.5506768435545127</v>
       </c>
@@ -11793,9 +11733,6 @@
       <c r="O63" t="n">
         <v>39</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.740565410297448</v>
       </c>
@@ -12337,9 +12274,6 @@
       <c r="O66" t="n">
         <v>47</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.8924762636917963</v>
       </c>
@@ -12881,9 +12815,6 @@
       <c r="O69" t="n">
         <v>26</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.4937102735316321</v>
       </c>
@@ -13425,9 +13356,6 @@
       <c r="O72" t="n">
         <v>26</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.4937102735316321</v>
       </c>
@@ -13969,9 +13897,6 @@
       <c r="O75" t="n">
         <v>50</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.9454101283677873</v>
       </c>
@@ -14513,9 +14438,6 @@
       <c r="O78" t="n">
         <v>28</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.5294296718859608</v>
       </c>
@@ -15057,9 +14979,6 @@
       <c r="O81" t="n">
         <v>48</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.9075937232330759</v>
       </c>
@@ -15601,9 +15520,6 @@
       <c r="O84" t="n">
         <v>53</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>1.002134736069854</v>
       </c>
@@ -16145,9 +16061,6 @@
       <c r="O87" t="n">
         <v>59</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>1.115583951473989</v>
       </c>
@@ -16689,9 +16602,6 @@
       <c r="O90" t="n">
         <v>53</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>1.002134736069854</v>
       </c>
@@ -17233,9 +17143,6 @@
       <c r="O93" t="n">
         <v>35</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.661787089857451</v>
       </c>
@@ -17777,9 +17684,6 @@
       <c r="O96" t="n">
         <v>37</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.6996034949921626</v>
       </c>
@@ -18321,9 +18225,6 @@
       <c r="O99" t="n">
         <v>46</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.8697773180983642</v>
       </c>
@@ -18865,9 +18766,6 @@
       <c r="O102" t="n">
         <v>46</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.8697773180983642</v>
       </c>
@@ -19409,9 +19307,6 @@
       <c r="O105" t="n">
         <v>43</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.8130527103962971</v>
       </c>
@@ -19953,9 +19848,6 @@
       <c r="O108" t="n">
         <v>20</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.3781640513471149</v>
       </c>
@@ -20497,9 +20389,6 @@
       <c r="O111" t="n">
         <v>55</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>1.0351232370675</v>
       </c>
@@ -21041,9 +20930,6 @@
       <c r="O114" t="n">
         <v>29</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.5457922522719544</v>
       </c>
@@ -21585,9 +21471,6 @@
       <c r="O117" t="n">
         <v>33</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.6210739422404997</v>
       </c>
@@ -22129,9 +22012,6 @@
       <c r="O120" t="n">
         <v>43</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.8092781671618634</v>
       </c>
@@ -22673,9 +22553,6 @@
       <c r="O123" t="n">
         <v>59</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>1.110404927036045</v>
       </c>
@@ -23217,9 +23094,6 @@
       <c r="O126" t="n">
         <v>49</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.9222007021146814</v>
       </c>
@@ -23761,9 +23635,6 @@
       <c r="O129" t="n">
         <v>51</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.9598415470989542</v>
       </c>
@@ -24305,9 +24176,6 @@
       <c r="O132" t="n">
         <v>40</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.7528168996854543</v>
       </c>
@@ -24849,9 +24717,6 @@
       <c r="O135" t="n">
         <v>32</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.6022535197483634</v>
       </c>
@@ -25393,9 +25258,6 @@
       <c r="O138" t="n">
         <v>39</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.733996477193318</v>
       </c>
@@ -25937,9 +25799,6 @@
       <c r="O141" t="n">
         <v>37</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.6963556322090453</v>
       </c>
@@ -26481,9 +26340,6 @@
       <c r="O144" t="n">
         <v>52</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.9786619695910906</v>
       </c>
@@ -27025,9 +26881,6 @@
       <c r="O147" t="n">
         <v>40</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.7492241081962028</v>
       </c>
@@ -27569,9 +27422,6 @@
       <c r="O150" t="n">
         <v>32</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.5993792865569622</v>
       </c>
@@ -28113,9 +27963,6 @@
       <c r="O153" t="n">
         <v>45</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.8428771217207279</v>
       </c>
@@ -28657,9 +28504,6 @@
       <c r="O156" t="n">
         <v>54</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>1.011452546064874</v>
       </c>
@@ -29201,9 +29045,6 @@
       <c r="O159" t="n">
         <v>48</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.8990689298354432</v>
       </c>
@@ -29745,9 +29586,6 @@
       <c r="O162" t="n">
         <v>55</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>1.030183148769779</v>
       </c>
@@ -30289,9 +30127,6 @@
       <c r="O165" t="n">
         <v>45</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.8428771217207279</v>
       </c>
@@ -30833,9 +30668,6 @@
       <c r="O168" t="n">
         <v>47</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.8803383271305381</v>
       </c>
@@ -31377,9 +31209,6 @@
       <c r="O171" t="n">
         <v>53</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.9927219433599686</v>
       </c>
@@ -31921,9 +31750,6 @@
       <c r="O174" t="n">
         <v>59</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>1.105105559589399</v>
       </c>
@@ -32465,9 +32291,6 @@
       <c r="O177" t="n">
         <v>43</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.8054159163109178</v>
       </c>
@@ -33008,9 +32831,6 @@
       </c>
       <c r="O180" t="n">
         <v>40</v>
-      </c>
-      <c r="Q180" t="n">
-        <v>0</v>
       </c>
       <c r="R180" t="n">
         <v>0.7492241081962028</v>
